--- a/SpringGame_2026/コスト表.xlsx
+++ b/SpringGame_2026/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\Program\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D38FAE9-ECE5-40D5-BC72-FD79B4A9ACD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9706C05-69FC-402C-A946-007CBEB44BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1125" windowWidth="25140" windowHeight="13320" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="1425" yWindow="-15225" windowWidth="25140" windowHeight="13320" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -222,7 +222,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,18 +232,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33CCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -261,72 +249,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -359,21 +287,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -381,15 +294,6 @@
       </top>
       <bottom style="thin">
         <color theme="2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
       </bottom>
       <diagonal/>
     </border>
@@ -404,148 +308,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -555,13 +324,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -570,165 +333,45 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1065,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="B1:T74"/>
+  <dimension ref="B1:U74"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
@@ -1086,21 +729,29 @@
     <col min="19" max="19" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B2" s="64" t="s">
+    <row r="1" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+    </row>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1108,76 +759,116 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
       <c r="H2" s="1"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B3" s="64"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B3" s="12"/>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="1"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B4" s="64"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B4" s="12"/>
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="1"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B5" s="64"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B5" s="12"/>
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
       <c r="H5" s="1"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B6" s="64"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B6" s="12"/>
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
       <c r="H6" s="1"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B7" s="64" t="s">
+      <c r="J6" s="18"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B7" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1185,34 +876,48 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="1"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B8" s="64" t="s">
+      <c r="J7" s="19"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B8" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B9" s="64" t="s">
+      <c r="I8" s="6"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B9" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1220,102 +925,121 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B10" s="64"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B10" s="12"/>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B11" s="64"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B11" s="12"/>
       <c r="C11" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
       <c r="H11" s="1"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B12" s="64"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B12" s="12"/>
       <c r="C12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B13" s="64"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B13" s="12"/>
       <c r="C13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B14" s="64" t="s">
+      <c r="I13" s="10"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B14" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1323,62 +1047,71 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B15" s="48"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B15" s="11"/>
       <c r="C15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B16" s="48"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B16" s="11"/>
       <c r="C16" s="3"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B17" s="48" t="s">
+      <c r="I16" s="6"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B17" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1386,57 +1119,73 @@
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B18" s="48"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B18" s="11"/>
       <c r="C18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="65"/>
+      <c r="F18" s="13"/>
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B19" s="48"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B19" s="11"/>
       <c r="C19" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="65"/>
+      <c r="F19" s="13"/>
       <c r="G19" s="2"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B20" s="48" t="s">
+      <c r="I19" s="6"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B20" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1444,41 +1193,48 @@
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="65"/>
+      <c r="F20" s="13"/>
       <c r="G20" s="2"/>
       <c r="H20" s="1"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B21" s="48"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B21" s="11"/>
       <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="F21" s="65"/>
+      <c r="F21" s="13"/>
       <c r="G21" s="2"/>
       <c r="H21" s="1"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B22" s="48" t="s">
+      <c r="J21" s="18"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1486,98 +1242,129 @@
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="65"/>
+      <c r="F22" s="13"/>
       <c r="G22" s="2"/>
       <c r="H22" s="1"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B23" s="48"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B23" s="11"/>
       <c r="C23" s="3"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="65"/>
+      <c r="F23" s="13"/>
       <c r="G23" s="2"/>
       <c r="H23" s="1"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-    </row>
-    <row r="24" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="48"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B24" s="11"/>
       <c r="C24" s="3"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="65"/>
+      <c r="F24" s="13"/>
       <c r="G24" s="2"/>
       <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="48"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B25" s="11"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="1"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="33"/>
-      <c r="R25" s="59"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="60"/>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B26" s="48"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B26" s="11"/>
       <c r="C26" s="3"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="1"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="36"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B27" s="48"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B27" s="11"/>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="1"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="39"/>
-      <c r="R27" s="61"/>
-      <c r="S27" s="61"/>
-      <c r="T27" s="61"/>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B28" s="48" t="s">
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B28" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -1588,19 +1375,21 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="1"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="39"/>
-      <c r="R28" s="62"/>
-      <c r="S28" s="62"/>
-      <c r="T28" s="62"/>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B29" s="48"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B29" s="11"/>
       <c r="C29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1609,16 +1398,21 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="1"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="42"/>
-    </row>
-    <row r="30" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B30" s="48"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B30" s="11"/>
       <c r="C30" s="3" t="s">
         <v>23</v>
       </c>
@@ -1627,124 +1421,168 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="1"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="45"/>
-      <c r="R30" s="63"/>
-      <c r="S30" s="63"/>
-    </row>
-    <row r="31" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="48"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B31" s="11"/>
       <c r="C31" s="3"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="1"/>
-      <c r="J31" s="32"/>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B32" s="48"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B32" s="11"/>
       <c r="C32" s="3"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="1"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="36"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B33" s="48"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B33" s="11"/>
       <c r="C33" s="3"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="1"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="49"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B34" s="48"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B34" s="11"/>
       <c r="C34" s="3"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="1"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="51"/>
-      <c r="N34" s="51"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="52"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B35" s="48"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B35" s="11"/>
       <c r="C35" s="3"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="1"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="55"/>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B36" s="48"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B36" s="11"/>
       <c r="C36" s="3"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="1"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="55"/>
-    </row>
-    <row r="37" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="48"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B37" s="11"/>
       <c r="C37" s="3"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="1"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="57"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="57"/>
-      <c r="P37" s="58"/>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B38" s="48"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B38" s="11"/>
       <c r="C38" s="3"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1752,8 +1590,8 @@
       <c r="G38" s="2"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B39" s="48"/>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B39" s="11"/>
       <c r="C39" s="3"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -1761,58 +1599,58 @@
       <c r="G39" s="2"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B40" s="48"/>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B40" s="11"/>
       <c r="C40" s="3"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="1"/>
-      <c r="K40" s="7"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B41" s="48"/>
+      <c r="K40" s="5"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B41" s="11"/>
       <c r="C41" s="3"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="1"/>
-      <c r="K41" s="7"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B42" s="48"/>
+      <c r="K41" s="5"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B42" s="11"/>
       <c r="C42" s="3"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="1"/>
-      <c r="K42" s="7"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B43" s="48"/>
+      <c r="K42" s="5"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B43" s="11"/>
       <c r="C43" s="3"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="1"/>
-      <c r="K43" s="7"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B44" s="48"/>
+      <c r="K43" s="5"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B44" s="11"/>
       <c r="C44" s="3"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="1"/>
-      <c r="K44" s="7"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B45" s="48"/>
+      <c r="K44" s="5"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B45" s="11"/>
       <c r="C45" s="3"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -1820,8 +1658,8 @@
       <c r="G45" s="2"/>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B46" s="48"/>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B46" s="11"/>
       <c r="C46" s="3"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -1829,8 +1667,8 @@
       <c r="G46" s="2"/>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B47" s="48"/>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B47" s="11"/>
       <c r="C47" s="3"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -1838,8 +1676,8 @@
       <c r="G47" s="2"/>
       <c r="H47" s="1"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B48" s="48"/>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.4">
+      <c r="B48" s="11"/>
       <c r="C48" s="3"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -1848,7 +1686,7 @@
       <c r="H48" s="1"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B49" s="48"/>
+      <c r="B49" s="11"/>
       <c r="C49" s="3"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -1857,7 +1695,7 @@
       <c r="H49" s="1"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B50" s="48"/>
+      <c r="B50" s="11"/>
       <c r="C50" s="3"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -1866,7 +1704,7 @@
       <c r="H50" s="1"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B51" s="48"/>
+      <c r="B51" s="11"/>
       <c r="C51" s="3"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1875,7 +1713,7 @@
       <c r="H51" s="1"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B52" s="48"/>
+      <c r="B52" s="11"/>
       <c r="C52" s="3"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -1884,7 +1722,7 @@
       <c r="H52" s="1"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B53" s="48"/>
+      <c r="B53" s="11"/>
       <c r="C53" s="3"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -1893,7 +1731,7 @@
       <c r="H53" s="1"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B54" s="48"/>
+      <c r="B54" s="11"/>
       <c r="C54" s="3"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1902,7 +1740,7 @@
       <c r="H54" s="1"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B55" s="48"/>
+      <c r="B55" s="11"/>
       <c r="C55" s="3"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -1911,7 +1749,7 @@
       <c r="H55" s="1"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B56" s="48"/>
+      <c r="B56" s="11"/>
       <c r="C56" s="3"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -1920,7 +1758,7 @@
       <c r="H56" s="1"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B57" s="48"/>
+      <c r="B57" s="11"/>
       <c r="C57" s="3"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -1929,7 +1767,7 @@
       <c r="H57" s="1"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B58" s="48"/>
+      <c r="B58" s="11"/>
       <c r="C58" s="3"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -1938,7 +1776,7 @@
       <c r="H58" s="1"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B59" s="48"/>
+      <c r="B59" s="11"/>
       <c r="C59" s="3"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -1947,7 +1785,7 @@
       <c r="H59" s="1"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B60" s="48"/>
+      <c r="B60" s="11"/>
       <c r="C60" s="3"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -1956,7 +1794,7 @@
       <c r="H60" s="1"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B61" s="48"/>
+      <c r="B61" s="11"/>
       <c r="C61" s="3"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -1965,7 +1803,7 @@
       <c r="H61" s="1"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B62" s="48"/>
+      <c r="B62" s="11"/>
       <c r="C62" s="3"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -1974,7 +1812,7 @@
       <c r="H62" s="1"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B63" s="48"/>
+      <c r="B63" s="11"/>
       <c r="C63" s="3"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -1983,7 +1821,7 @@
       <c r="H63" s="1"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B64" s="48"/>
+      <c r="B64" s="11"/>
       <c r="C64" s="3"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -1992,7 +1830,7 @@
       <c r="H64" s="1"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B65" s="48"/>
+      <c r="B65" s="11"/>
       <c r="C65" s="3"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2001,7 +1839,7 @@
       <c r="H65" s="1"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B66" s="48"/>
+      <c r="B66" s="11"/>
       <c r="C66" s="3"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -2010,7 +1848,7 @@
       <c r="H66" s="1"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B67" s="48"/>
+      <c r="B67" s="11"/>
       <c r="C67" s="3"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -2019,7 +1857,7 @@
       <c r="H67" s="1"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B68" s="48"/>
+      <c r="B68" s="11"/>
       <c r="C68" s="3"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -2028,7 +1866,7 @@
       <c r="H68" s="1"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B69" s="48"/>
+      <c r="B69" s="11"/>
       <c r="C69" s="3"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -2037,7 +1875,7 @@
       <c r="H69" s="1"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B70" s="48"/>
+      <c r="B70" s="11"/>
       <c r="C70" s="3"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -2046,7 +1884,7 @@
       <c r="H70" s="1"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B71" s="48"/>
+      <c r="B71" s="11"/>
       <c r="C71" s="3"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2055,7 +1893,7 @@
       <c r="H71" s="1"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B72" s="48"/>
+      <c r="B72" s="11"/>
       <c r="C72" s="3"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -2064,7 +1902,7 @@
       <c r="H72" s="1"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B73" s="48"/>
+      <c r="B73" s="11"/>
       <c r="C73" s="3"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>

--- a/SpringGame_2026/コスト表.xlsx
+++ b/SpringGame_2026/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81EA613-9133-40B7-AC3A-14D6ED0C1AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14EA8EE-DC25-47D2-A68D-0718943EE9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="57">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -353,6 +353,13 @@
     <t>1日で3コスト</t>
     <rPh sb="1" eb="2">
       <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 　未完了</t>
+    <rPh sb="2" eb="5">
+      <t>ミカンリョウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -657,7 +664,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -696,13 +703,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -713,7 +714,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -759,6 +760,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1094,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="B1:R70"/>
+  <dimension ref="B1:R69"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
@@ -1123,25 +1127,25 @@
       </c>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="18" t="s">
         <v>43</v>
       </c>
       <c r="J2" s="10"/>
@@ -1166,16 +1170,16 @@
         <v>1</v>
       </c>
       <c r="G3" s="4"/>
-      <c r="H3" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="26" t="s">
+      <c r="H3" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="24" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1194,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="20" t="s">
         <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -1221,10 +1225,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="23" t="s">
+      <c r="H5" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="21" t="s">
         <v>38</v>
       </c>
       <c r="K5" s="2">
@@ -1248,10 +1252,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="4"/>
-      <c r="H6" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="24" t="s">
+      <c r="H6" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="22" t="s">
         <v>39</v>
       </c>
       <c r="K6" s="2">
@@ -1269,10 +1273,10 @@
       <c r="E7" s="1"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="25" t="s">
+      <c r="H7" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="23" t="s">
         <v>41</v>
       </c>
       <c r="K7" s="2">
@@ -1296,17 +1300,17 @@
         <v>1</v>
       </c>
       <c r="G8" s="4"/>
-      <c r="H8" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="28" t="s">
+      <c r="H8" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="26" t="s">
         <v>42</v>
       </c>
       <c r="K8" s="2">
         <f>COUNTIF(H3:H40,J8)</f>
-        <v>38</v>
-      </c>
-      <c r="L8" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="L8" s="14"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B9" s="8" t="s">
@@ -1317,17 +1321,17 @@
       <c r="E9" s="1"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="27" t="s">
+      <c r="H9" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="14">
         <f>COUNTIF(H3:H40,J9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="15"/>
+      <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
@@ -1346,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="4"/>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="20" t="s">
         <v>42</v>
       </c>
       <c r="I10" s="6"/>
@@ -1372,10 +1376,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="14"/>
+      <c r="H11" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="6"/>
       <c r="J11" s="12"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
@@ -1396,12 +1400,12 @@
       <c r="F12" s="4">
         <v>1</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="35"/>
-      <c r="J12" s="30"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="33"/>
+      <c r="J12" s="28"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
@@ -1425,13 +1429,13 @@
       <c r="F13" s="4">
         <v>1</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="35"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="33"/>
       <c r="J13" s="11"/>
-      <c r="K13" s="29"/>
+      <c r="K13" s="27"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
@@ -1454,11 +1458,11 @@
       <c r="F14" s="4">
         <v>1</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="35"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="33"/>
       <c r="J14" s="11"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
@@ -1485,11 +1489,11 @@
       <c r="F15" s="4">
         <v>1</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="35"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="33"/>
       <c r="J15" s="11"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
@@ -1514,11 +1518,11 @@
       <c r="F16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="35"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="33"/>
       <c r="J16" s="11"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
@@ -1537,11 +1541,11 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="36"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="34"/>
       <c r="J17" s="11"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
@@ -1567,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="4"/>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="30" t="s">
         <v>42</v>
       </c>
       <c r="I18" s="6"/>
@@ -1589,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="2"/>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="20" t="s">
         <v>42</v>
       </c>
       <c r="I19" s="6"/>
@@ -1618,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="20" t="s">
         <v>42</v>
       </c>
       <c r="I20" s="6"/>
@@ -1641,7 +1645,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="20" t="s">
         <v>42</v>
       </c>
       <c r="I21" s="6"/>
@@ -1670,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="20" t="s">
         <v>42</v>
       </c>
       <c r="I22" s="6"/>
@@ -1699,7 +1703,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="20" t="s">
         <v>42</v>
       </c>
       <c r="J23" s="11"/>
@@ -1720,7 +1724,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="20" t="s">
         <v>42</v>
       </c>
       <c r="J24" s="11"/>
@@ -1747,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="2"/>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="20" t="s">
         <v>42</v>
       </c>
       <c r="J25" s="11"/>
@@ -1774,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="20" t="s">
         <v>42</v>
       </c>
       <c r="J26" s="11"/>
@@ -1801,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="2"/>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="20" t="s">
         <v>42</v>
       </c>
       <c r="J27" s="11"/>
@@ -1822,7 +1826,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="20" t="s">
         <v>42</v>
       </c>
       <c r="J28" s="11"/>
@@ -1849,7 +1853,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="2"/>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1868,7 +1872,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="2"/>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1887,7 +1891,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="2"/>
-      <c r="H31" s="22" t="s">
+      <c r="H31" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1900,7 +1904,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1919,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="2"/>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1938,7 +1942,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="2"/>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1957,7 +1961,7 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="2"/>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1976,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="2"/>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="20" t="s">
         <v>42</v>
       </c>
       <c r="K36" s="5"/>
@@ -1990,7 +1994,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="22" t="s">
+      <c r="H37" s="20" t="s">
         <v>42</v>
       </c>
       <c r="K37" s="5"/>
@@ -2010,7 +2014,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="2"/>
-      <c r="H38" s="22" t="s">
+      <c r="H38" s="20" t="s">
         <v>42</v>
       </c>
       <c r="K38" s="5"/>
@@ -2030,7 +2034,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="2"/>
-      <c r="H39" s="22" t="s">
+      <c r="H39" s="20" t="s">
         <v>42</v>
       </c>
       <c r="K39" s="5"/>
@@ -2050,265 +2054,122 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="2"/>
-      <c r="H40" s="22" t="s">
+      <c r="H40" s="20" t="s">
         <v>42</v>
       </c>
       <c r="K40" s="5"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
-      <c r="H61" s="16"/>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
-      <c r="H62" s="16"/>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
-      <c r="H63" s="16"/>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
-      <c r="H66" s="16"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
-      <c r="H68" s="16"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="C70" s="16"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+    </row>
+    <row r="63" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/SpringGame_2026/コスト表.xlsx
+++ b/SpringGame_2026/コスト表.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14EA8EE-DC25-47D2-A68D-0718943EE9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8377AEA-AE4C-4997-B580-F4CBCF6D9A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="コスト表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="54">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>タイトル</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>インゲーム</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -120,10 +116,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ジャンプ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>カメラ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -311,14 +303,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>UI</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クリア</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>完了</t>
     <rPh sb="0" eb="2">
       <t>カンリョウ</t>
@@ -350,16 +334,23 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>1日で3コスト</t>
-    <rPh sb="1" eb="2">
-      <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 　未完了</t>
     <rPh sb="2" eb="5">
       <t>ミカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1日で2コスト</t>
+    <rPh sb="1" eb="2">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>回避</t>
+    <rPh sb="0" eb="2">
+      <t>カイヒ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -473,7 +464,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -561,19 +552,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -733,24 +711,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -758,11 +736,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1098,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="B1:R69"/>
+  <dimension ref="B1:R64"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
@@ -1120,33 +1098,33 @@
   <sheetData>
     <row r="1" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="17" t="s">
+      <c r="F2" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="H2" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
@@ -1161,197 +1139,205 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.5</v>
       </c>
       <c r="G3" s="4"/>
-      <c r="H3" s="38" t="s">
-        <v>56</v>
+      <c r="H3" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B4" s="8"/>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.5</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K4" s="2">
-        <f>SUM(F3:F40)</f>
-        <v>30.5</v>
+        <f>SUM(F3:F36)</f>
+        <v>26.5</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B5" s="8"/>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.5</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K5" s="2">
-        <f>SUMIF(E3:E40,"プロト",F3:F40)</f>
-        <v>15</v>
-      </c>
-      <c r="L5" s="2"/>
+        <f>SUMIF(E3:E36,"プロト",F3:F36)</f>
+        <v>13.5</v>
+      </c>
+      <c r="L5" s="2">
+        <f>SUMIF(E3:E36,"プロト",F3:F36)</f>
+        <v>13.5</v>
+      </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B6" s="8"/>
       <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="20" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="38">
+        <v>1</v>
+      </c>
+      <c r="G6" s="38"/>
+      <c r="H6" s="37" t="s">
+        <v>40</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2">
-        <f>SUMIF(E3:E40,"アルファ",F3:F40)</f>
-        <v>13</v>
-      </c>
-      <c r="L6" s="2"/>
+        <f>SUMIF(E3:E36,"アルファ",F3:F36)</f>
+        <v>12</v>
+      </c>
+      <c r="L6" s="2">
+        <f>SUMIF(E3:E36,"アルファ",F3:F36)</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B7" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="20" t="s">
-        <v>42</v>
-      </c>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="37"/>
       <c r="J7" s="23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K7" s="2">
-        <f>SUMIF(E3:E40,"ベータ",F3:F40)</f>
-        <v>2.5</v>
-      </c>
-      <c r="L7" s="2"/>
+        <f>SUMIF(E3:E36,"ベータ",F3:F36)</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <f>SUMIF(E3:E36,"ベータ",F3:F36)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="2"/>
       <c r="H8" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2">
-        <f>COUNTIF(H3:H40,J8)</f>
-        <v>37</v>
-      </c>
-      <c r="L8" s="14"/>
+        <f>COUNTIF(H3:H36,J8)</f>
+        <v>32</v>
+      </c>
+      <c r="L8" s="2">
+        <f>COUNTIF(H3:H36,J8)</f>
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B9" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="4"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.5</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K9" s="14">
-        <f>COUNTIF(H3:H40,J9)</f>
+        <f>COUNTIF(H3:H36,J9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="14"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="13"/>
@@ -1362,22 +1348,24 @@
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="C11" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="29" t="s">
-        <v>42</v>
+      <c r="H11" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="12"/>
@@ -1389,22 +1377,22 @@
     <row r="12" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B12" s="8"/>
       <c r="C12" s="3" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="33"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="32"/>
       <c r="J12" s="28"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
@@ -1418,22 +1406,22 @@
     <row r="13" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B13" s="8"/>
       <c r="C13" s="3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="33"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" s="32"/>
       <c r="J13" s="11"/>
       <c r="K13" s="27"/>
       <c r="L13" s="6"/>
@@ -1447,22 +1435,22 @@
     <row r="14" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B14" s="8"/>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
       </c>
-      <c r="G14" s="32"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="33"/>
+        <v>40</v>
+      </c>
+      <c r="I14" s="32"/>
       <c r="J14" s="11"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
@@ -1474,26 +1462,24 @@
       <c r="R14" s="6"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B15" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="B15" s="8"/>
       <c r="C15" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F15" s="4">
         <v>1</v>
       </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="33"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="32"/>
       <c r="J15" s="11"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
@@ -1505,24 +1491,26 @@
       <c r="R15" s="6"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B16" s="7"/>
+      <c r="B16" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="C16" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="33"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="32"/>
       <c r="J16" s="11"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
@@ -1534,18 +1522,24 @@
       <c r="R16" s="6"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="2"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
       <c r="G17" s="31"/>
-      <c r="H17" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="34"/>
+      <c r="H17" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="33"/>
       <c r="J17" s="11"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
@@ -1557,44 +1551,45 @@
       <c r="R17" s="6"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B18" s="7"/>
-      <c r="C18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="30" t="s">
-        <v>42</v>
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="35" t="s">
+        <v>40</v>
       </c>
       <c r="I18" s="6"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B19" s="7"/>
       <c r="C19" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F19" s="9">
         <v>1</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="10"/>
@@ -1607,38 +1602,38 @@
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B20" s="7"/>
       <c r="C20" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F20" s="9">
         <v>1</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
       <c r="N20" s="6"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B21" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="1"/>
@@ -1646,7 +1641,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="11"/>
@@ -1662,27 +1657,25 @@
     <row r="22" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B22" s="7"/>
       <c r="C22" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F22" s="9">
         <v>1</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="6"/>
+        <v>40</v>
+      </c>
       <c r="J22" s="11"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
       <c r="O22" s="11"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
@@ -1691,20 +1684,20 @@
     <row r="23" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B23" s="7"/>
       <c r="C23" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F23" s="9">
         <v>1</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="6"/>
@@ -1717,7 +1710,7 @@
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B24" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="1"/>
@@ -1725,7 +1718,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="6"/>
@@ -1739,20 +1732,20 @@
     <row r="25" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B25" s="7"/>
       <c r="C25" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F25" s="9">
         <v>1</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="6"/>
@@ -1766,20 +1759,20 @@
     <row r="26" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B26" s="7"/>
       <c r="C26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="F26" s="9">
         <v>1</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="6"/>
@@ -1793,20 +1786,20 @@
     <row r="27" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B27" s="7"/>
       <c r="C27" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F27" s="9">
         <v>1</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J27" s="11"/>
       <c r="K27" s="6"/>
@@ -1817,9 +1810,9 @@
       <c r="Q27" s="6"/>
       <c r="R27" s="6"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B28" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="1"/>
@@ -1827,16 +1820,8 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="11"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
+        <v>40</v>
+      </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B29" s="7"/>
@@ -1844,60 +1829,60 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F29" s="2">
         <v>2</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B30" s="7"/>
       <c r="C30" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B31" s="7"/>
       <c r="C31" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F31" s="2">
         <v>2</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B32" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="1"/>
@@ -1905,159 +1890,105 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B33" s="7"/>
       <c r="C33" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B34" s="7"/>
       <c r="C34" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F34" s="2">
         <v>0.5</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B35" s="7"/>
       <c r="C35" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F35" s="2">
         <v>0.5</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="20" t="s">
-        <v>42</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="K35" s="5"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B36" s="7"/>
       <c r="C36" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="K36" s="5"/>
+        <v>40</v>
+      </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B37" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="K37" s="5"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B38" s="7"/>
-      <c r="C38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="K38" s="5"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B39" s="7"/>
-      <c r="C39" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="K39" s="5"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B40" s="7"/>
-      <c r="C40" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="K40" s="5"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.4">
       <c r="D42" s="19"/>
@@ -2151,33 +2082,13 @@
       <c r="D64" s="19"/>
       <c r="E64" s="19"/>
     </row>
-    <row r="65" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-    </row>
-    <row r="66" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-    </row>
-    <row r="67" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-    </row>
-    <row r="68" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-    </row>
-    <row r="69" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K7 D42:D69 D3:D40" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D64" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42:E69 E3:E40" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E64" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
   </dataValidations>

--- a/SpringGame_2026/コスト表.xlsx
+++ b/SpringGame_2026/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8377AEA-AE4C-4997-B580-F4CBCF6D9A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3E83C1-C821-49FA-B258-8C0B932C7937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="64">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -199,16 +199,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ステージの当たり判定</t>
-    <rPh sb="5" eb="6">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>キャラクターの当たり判定</t>
     <rPh sb="7" eb="8">
       <t>ア</t>
@@ -351,6 +341,57 @@
     <t>回避</t>
     <rPh sb="0" eb="2">
       <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1日の消費コスト</t>
+    <rPh sb="1" eb="2">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>残り日数</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニッスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3月</t>
+  </si>
+  <si>
+    <t>日</t>
+  </si>
+  <si>
+    <t>月</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>木</t>
+  </si>
+  <si>
+    <t>金</t>
+  </si>
+  <si>
+    <t>土</t>
+  </si>
+  <si>
+    <t>4月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -464,7 +505,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -543,15 +584,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="3" tint="0.89999084444715716"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -642,7 +674,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -708,24 +740,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -733,14 +765,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1076,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="B1:R64"/>
+  <dimension ref="B1:T63"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
@@ -1084,27 +1120,26 @@
     <col min="4" max="6" width="11.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.75" customWidth="1"/>
-    <col min="14" max="14" width="7.5" customWidth="1"/>
-    <col min="15" max="15" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.75" customWidth="1"/>
-    <col min="17" max="17" width="7.5" customWidth="1"/>
-    <col min="18" max="18" width="7.625" customWidth="1"/>
-    <col min="19" max="19" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="16.875" customWidth="1"/>
+    <col min="15" max="15" width="9.875" customWidth="1"/>
+    <col min="16" max="16" width="12.375" customWidth="1"/>
+    <col min="17" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="9.625" customWidth="1"/>
+    <col min="19" max="19" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B2" s="15" t="s">
         <v>21</v>
       </c>
@@ -1124,14 +1159,14 @@
         <v>26</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
@@ -1139,195 +1174,320 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="2">
         <v>0.5</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="6"/>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B4" s="8"/>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2">
         <v>0.5</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K4" s="2">
-        <f>SUM(F3:F36)</f>
-        <v>26.5</v>
+        <f>SUM(F3:F35)</f>
+        <v>23.5</v>
       </c>
       <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="N4" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q4" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4" s="39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B5" s="8"/>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="2">
         <v>0.5</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K5" s="2">
-        <f>SUMIF(E3:E36,"プロト",F3:F36)</f>
-        <v>13.5</v>
+        <f>SUMIF(E3:E35,"プロト",F3:F35)</f>
+        <v>12.5</v>
       </c>
       <c r="L5" s="2">
-        <f>SUMIF(E3:E36,"プロト",F3:F36)</f>
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.4">
+        <f>SUMIF(E3:E35,"プロト",F3:F35)</f>
+        <v>12.5</v>
+      </c>
+      <c r="N5" s="6">
+        <v>1</v>
+      </c>
+      <c r="O5" s="6">
+        <v>2</v>
+      </c>
+      <c r="P5" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>4</v>
+      </c>
+      <c r="R5" s="6">
+        <v>5</v>
+      </c>
+      <c r="S5" s="6">
+        <v>6</v>
+      </c>
+      <c r="T5" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B6" s="8"/>
       <c r="C6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="38">
+        <v>52</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="37">
         <v>1</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="37" t="s">
-        <v>40</v>
+      <c r="G6" s="37"/>
+      <c r="H6" s="36" t="s">
+        <v>39</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K6" s="2">
-        <f>SUMIF(E3:E36,"アルファ",F3:F36)</f>
+        <f>SUMIF(E3:E35,"アルファ",F3:F35)</f>
+        <v>10</v>
+      </c>
+      <c r="L6" s="2">
+        <f>SUMIF(E3:E35,"アルファ",F3:F35)</f>
+        <v>10</v>
+      </c>
+      <c r="N6" s="6">
+        <v>8</v>
+      </c>
+      <c r="O6" s="6">
+        <v>9</v>
+      </c>
+      <c r="P6" s="6">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>11</v>
+      </c>
+      <c r="R6" s="6">
         <v>12</v>
       </c>
-      <c r="L6" s="2">
-        <f>SUMIF(E3:E36,"アルファ",F3:F36)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="S6" s="6">
+        <v>13</v>
+      </c>
+      <c r="T6" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="37"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="36"/>
       <c r="J7" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K7" s="2">
-        <f>SUMIF(E3:E36,"ベータ",F3:F36)</f>
+        <f>SUMIF(E3:E35,"ベータ",F3:F35)</f>
         <v>1</v>
       </c>
       <c r="L7" s="2">
-        <f>SUMIF(E3:E36,"ベータ",F3:F36)</f>
+        <f>SUMIF(E3:E35,"ベータ",F3:F35)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="N7" s="38">
+        <v>15</v>
+      </c>
+      <c r="O7" s="6">
+        <v>16</v>
+      </c>
+      <c r="P7" s="6">
+        <v>17</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>18</v>
+      </c>
+      <c r="R7" s="6">
+        <v>19</v>
+      </c>
+      <c r="S7" s="38">
+        <v>20</v>
+      </c>
+      <c r="T7" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2">
         <v>0.5</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8" s="2">
-        <f>COUNTIF(H3:H36,J8)</f>
-        <v>32</v>
+        <f>COUNTIF(H3:H35,J8)</f>
+        <v>31</v>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF(H3:H36,J8)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.4">
+        <f>COUNTIF(H3:H35,J8)</f>
+        <v>31</v>
+      </c>
+      <c r="N8" s="38">
+        <v>22</v>
+      </c>
+      <c r="O8" s="6">
+        <v>23</v>
+      </c>
+      <c r="P8" s="6">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>25</v>
+      </c>
+      <c r="R8" s="6">
+        <v>26</v>
+      </c>
+      <c r="S8" s="38">
+        <v>27</v>
+      </c>
+      <c r="T8" s="6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B9" s="8"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" s="2">
         <v>0.5</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="14">
-        <f>COUNTIF(H3:H36,J9)</f>
+        <f>COUNTIF(H3:H35,J9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="14"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="N9" s="38">
+        <v>29</v>
+      </c>
+      <c r="O9" s="6">
+        <v>30</v>
+      </c>
+      <c r="P9" s="6">
+        <v>31</v>
+      </c>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="6"/>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>0</v>
       </c>
@@ -1337,7 +1497,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="13"/>
@@ -1347,7 +1507,7 @@
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B11" s="8" t="s">
         <v>9</v>
       </c>
@@ -1355,75 +1515,96 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="J11" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" s="6">
+        <f ca="1">DATE(2026,4,13)-TODAY()</f>
+        <v>27</v>
+      </c>
       <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="N11" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B12" s="8"/>
       <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="4"/>
-      <c r="H12" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="32"/>
-      <c r="J12" s="28"/>
+      <c r="H12" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="31"/>
+      <c r="J12" s="27"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="6"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="Q12" s="10">
+        <v>1</v>
+      </c>
+      <c r="R12" s="10">
+        <v>2</v>
+      </c>
+      <c r="S12">
+        <v>3</v>
+      </c>
+      <c r="T12" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B13" s="8"/>
       <c r="C13" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" s="4">
-        <v>1</v>
-      </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="27"/>
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="31"/>
+      <c r="J13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="6">
+        <f ca="1">K4/K11</f>
+        <v>0.87037037037037035</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
@@ -1432,54 +1613,53 @@
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B14" s="8"/>
       <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="32"/>
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="31"/>
       <c r="J14" s="11"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="11"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B15" s="8"/>
       <c r="C15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" s="4">
         <v>1</v>
       </c>
-      <c r="G15" s="31"/>
-      <c r="H15" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="32"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="31"/>
       <c r="J15" s="11"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
@@ -1490,7 +1670,7 @@
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B16" s="8" t="s">
         <v>11</v>
       </c>
@@ -1498,55 +1678,41 @@
         <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="31"/>
-      <c r="H16" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="32"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="6"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="31"/>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B17" s="7"/>
       <c r="C17" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="4">
         <v>1</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="6"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="32"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
     </row>
@@ -1558,18 +1724,11 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="35" t="s">
-        <v>40</v>
+      <c r="G18" s="29"/>
+      <c r="H18" s="34" t="s">
+        <v>39</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
     </row>
@@ -1579,59 +1738,45 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" s="9">
         <v>1</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B20" s="7"/>
       <c r="C20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20" s="9">
         <v>1</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B21" s="7" t="s">
         <v>5</v>
       </c>
@@ -1641,43 +1786,30 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B22" s="7"/>
       <c r="C22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22" s="9">
         <v>1</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="J22" s="11"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="6"/>
+        <v>39</v>
+      </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
     </row>
@@ -1687,17 +1819,17 @@
         <v>13</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F23" s="9">
         <v>1</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="6"/>
@@ -1718,7 +1850,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="6"/>
@@ -1735,17 +1867,17 @@
         <v>15</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F25" s="9">
         <v>1</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="6"/>
@@ -1762,17 +1894,17 @@
         <v>27</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" s="9">
         <v>1</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="6"/>
@@ -1783,133 +1915,125 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B27" s="7"/>
-      <c r="C27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" s="9">
-        <v>1</v>
-      </c>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="J27" s="11"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
+        <v>39</v>
+      </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="2"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="2">
+        <v>2</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B29" s="7"/>
       <c r="C29" s="3" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" s="2">
         <v>2</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B30" s="7"/>
       <c r="C30" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B31" s="7"/>
-      <c r="C31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="2">
-        <v>2</v>
-      </c>
+      <c r="B31" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="2"/>
+      <c r="D32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
       <c r="G32" s="2"/>
       <c r="H32" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B33" s="7"/>
       <c r="C33" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.4">
@@ -1918,57 +2042,42 @@
         <v>42</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34" s="2">
         <v>0.5</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="20" t="s">
-        <v>40</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="K34" s="5"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B35" s="7"/>
       <c r="C35" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F35" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="K35" s="5"/>
+        <v>39</v>
+      </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B36" s="7"/>
-      <c r="C36" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="2">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="20" t="s">
-        <v>40</v>
-      </c>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.4">
       <c r="D37" s="19"/>
@@ -2078,17 +2187,13 @@
       <c r="D63" s="19"/>
       <c r="E63" s="19"/>
     </row>
-    <row r="64" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D64" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D63" xr:uid="{D99FF9D9-52C2-47CC-BC93-4ACF23B2DA2A}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E64" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E63" xr:uid="{3F25CF45-EEFF-4838-8184-2DB508A95967}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
   </dataValidations>

--- a/SpringGame_2026/コスト表.xlsx
+++ b/SpringGame_2026/コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3E83C1-C821-49FA-B258-8C0B932C7937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BEA9D2-32B4-4447-B7AE-D6F9EA739EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="4815" yWindow="1095" windowWidth="23760" windowHeight="13530" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="63">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -320,13 +320,6 @@
     <t>全体</t>
     <rPh sb="0" eb="2">
       <t>ゼンタイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 　未完了</t>
-    <rPh sb="2" eb="5">
-      <t>ミカンリョウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -674,7 +667,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -764,12 +757,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1136,7 +1123,7 @@
         <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="2:20" x14ac:dyDescent="0.35">
@@ -1182,9 +1169,11 @@
       <c r="F3" s="2">
         <v>0.5</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="2" t="s">
-        <v>50</v>
+      <c r="G3" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="J3" s="24" t="s">
         <v>34</v>
@@ -1196,7 +1185,7 @@
         <v>48</v>
       </c>
       <c r="N3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
@@ -1229,26 +1218,26 @@
         <v>23.5</v>
       </c>
       <c r="L4" s="2"/>
-      <c r="N4" s="40" t="s">
+      <c r="N4" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="O4" s="39" t="s">
+      <c r="P4" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="39" t="s">
+      <c r="Q4" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="39" t="s">
+      <c r="R4" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="39" t="s">
+      <c r="S4" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="S4" s="40" t="s">
+      <c r="T4" s="37" t="s">
         <v>61</v>
-      </c>
-      <c r="T4" s="39" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.4">
@@ -1305,19 +1294,19 @@
     <row r="6" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B6" s="8"/>
       <c r="C6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="9">
         <v>1</v>
       </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="36" t="s">
+      <c r="G6" s="9"/>
+      <c r="H6" s="20" t="s">
         <v>39</v>
       </c>
       <c r="J6" s="22" t="s">
@@ -1358,11 +1347,11 @@
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="36"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="20"/>
       <c r="J7" s="23" t="s">
         <v>38</v>
       </c>
@@ -1374,7 +1363,7 @@
         <f>SUMIF(E3:E35,"ベータ",F3:F35)</f>
         <v>1</v>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="36">
         <v>15</v>
       </c>
       <c r="O7" s="6">
@@ -1389,7 +1378,7 @@
       <c r="R7" s="6">
         <v>19</v>
       </c>
-      <c r="S7" s="38">
+      <c r="S7" s="36">
         <v>20</v>
       </c>
       <c r="T7" s="6">
@@ -1425,7 +1414,7 @@
         <f>COUNTIF(H3:H35,J8)</f>
         <v>31</v>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="36">
         <v>22</v>
       </c>
       <c r="O8" s="6">
@@ -1440,7 +1429,7 @@
       <c r="R8" s="6">
         <v>26</v>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="36">
         <v>27</v>
       </c>
       <c r="T8" s="6">
@@ -1470,10 +1459,10 @@
       </c>
       <c r="K9" s="14">
         <f>COUNTIF(H3:H35,J9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="14"/>
-      <c r="N9" s="38">
+      <c r="N9" s="36">
         <v>29</v>
       </c>
       <c r="O9" s="6">
@@ -1484,7 +1473,7 @@
       </c>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
-      <c r="S9" s="38"/>
+      <c r="S9" s="36"/>
       <c r="T9" s="6"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.4">
@@ -1529,7 +1518,7 @@
       </c>
       <c r="I11" s="6"/>
       <c r="J11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K11" s="6">
         <f ca="1">DATE(2026,4,13)-TODAY()</f>
@@ -1537,7 +1526,7 @@
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.4">
@@ -1599,7 +1588,7 @@
       </c>
       <c r="I13" s="31"/>
       <c r="J13" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K13" s="6">
         <f ca="1">K4/K11</f>

--- a/SpringGame_2026/コスト表.xlsx
+++ b/SpringGame_2026/コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OsakiTowa\Desktop\2026_SpringGame\SpringGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yongy\git\2026_SpringGame\SpringGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BEA9D2-32B4-4447-B7AE-D6F9EA739EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CD2797-95CA-441E-B795-E95BA8F2ECE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4815" yWindow="1095" windowWidth="23760" windowHeight="13530" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C536231-C66C-4A73-9D9A-B6DFFC0D3CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="64">
   <si>
     <t>アニメーション</t>
     <phoneticPr fontId="2"/>
@@ -385,6 +385,13 @@
     <t>4月</t>
     <rPh sb="1" eb="2">
       <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>完全提出</t>
+    <rPh sb="0" eb="4">
+      <t>カンゼンテイシュツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -436,7 +443,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -497,8 +504,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -576,17 +601,6 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="3" tint="0.89999084444715716"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.89999084444715716"/>
       </bottom>
       <diagonal/>
     </border>
@@ -661,13 +675,116 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -682,9 +799,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -700,9 +814,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -733,21 +844,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -755,15 +866,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1099,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039B1606-320D-4390-8B98-CE6030BB2FAA}">
-  <dimension ref="B1:T63"/>
+  <dimension ref="B1:R63"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
@@ -1118,7 +1315,7 @@
     <col min="19" max="19" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>30</v>
       </c>
@@ -1126,35 +1323,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B2" s="15" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B3" s="8" t="s">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1172,28 +1369,21 @@
       <c r="G3" s="4">
         <v>0.5</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="24" t="s">
+      <c r="L3" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="N3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="6"/>
-    </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B4" s="8"/>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B4" s="7"/>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1207,7 +1397,7 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="4"/>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -1218,30 +1408,9 @@
         <v>23.5</v>
       </c>
       <c r="L4" s="2"/>
-      <c r="N4" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="O4" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="P4" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q4" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="R4" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="S4" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="T4" s="37" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B5" s="8"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B5" s="7"/>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
@@ -1255,10 +1424,10 @@
         <v>0.5</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="21" t="s">
+      <c r="H5" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="19" t="s">
         <v>35</v>
       </c>
       <c r="K5" s="2">
@@ -1269,47 +1438,26 @@
         <f>SUMIF(E3:E35,"プロト",F3:F35)</f>
         <v>12.5</v>
       </c>
-      <c r="N5" s="6">
-        <v>1</v>
-      </c>
-      <c r="O5" s="6">
-        <v>2</v>
-      </c>
-      <c r="P5" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>4</v>
-      </c>
-      <c r="R5" s="6">
-        <v>5</v>
-      </c>
-      <c r="S5" s="6">
-        <v>6</v>
-      </c>
-      <c r="T5" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B6" s="8"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B6" s="7"/>
       <c r="C6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>1</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="22" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="20" t="s">
         <v>36</v>
       </c>
       <c r="K6" s="2">
@@ -1320,39 +1468,18 @@
         <f>SUMIF(E3:E35,"アルファ",F3:F35)</f>
         <v>10</v>
       </c>
-      <c r="N6" s="6">
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="6">
-        <v>9</v>
-      </c>
-      <c r="P6" s="6">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>11</v>
-      </c>
-      <c r="R6" s="6">
-        <v>12</v>
-      </c>
-      <c r="S6" s="6">
-        <v>13</v>
-      </c>
-      <c r="T6" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B7" s="8" t="s">
-        <v>8</v>
-      </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="20"/>
-      <c r="J7" s="23" t="s">
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="18"/>
+      <c r="J7" s="21" t="s">
         <v>38</v>
       </c>
       <c r="K7" s="2">
@@ -1363,30 +1490,9 @@
         <f>SUMIF(E3:E35,"ベータ",F3:F35)</f>
         <v>1</v>
       </c>
-      <c r="N7" s="36">
-        <v>15</v>
-      </c>
-      <c r="O7" s="6">
-        <v>16</v>
-      </c>
-      <c r="P7" s="6">
-        <v>17</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>18</v>
-      </c>
-      <c r="R7" s="6">
-        <v>19</v>
-      </c>
-      <c r="S7" s="36">
-        <v>20</v>
-      </c>
-      <c r="T7" s="6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B8" s="8"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B8" s="7"/>
       <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
@@ -1400,10 +1506,10 @@
         <v>0.5</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="26" t="s">
+      <c r="H8" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="24" t="s">
         <v>39</v>
       </c>
       <c r="K8" s="2">
@@ -1414,30 +1520,9 @@
         <f>COUNTIF(H3:H35,J8)</f>
         <v>31</v>
       </c>
-      <c r="N8" s="36">
-        <v>22</v>
-      </c>
-      <c r="O8" s="6">
-        <v>23</v>
-      </c>
-      <c r="P8" s="6">
-        <v>24</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>25</v>
-      </c>
-      <c r="R8" s="6">
-        <v>26</v>
-      </c>
-      <c r="S8" s="36">
-        <v>27</v>
-      </c>
-      <c r="T8" s="6">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B9" s="8"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B9" s="7"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1451,33 +1536,20 @@
         <v>0.5</v>
       </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="25" t="s">
+      <c r="H9" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="12">
         <f>COUNTIF(H3:H35,J9)</f>
         <v>1</v>
       </c>
-      <c r="L9" s="14"/>
-      <c r="N9" s="36">
-        <v>29</v>
-      </c>
-      <c r="O9" s="6">
-        <v>30</v>
-      </c>
-      <c r="P9" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="6"/>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B10" s="8" t="s">
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B10" s="7" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="3"/>
@@ -1485,19 +1557,17 @@
       <c r="E10" s="1"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B11" s="8" t="s">
+      <c r="H10" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1513,24 +1583,21 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="6"/>
+      <c r="H11" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="5"/>
       <c r="J11" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <f ca="1">DATE(2026,4,13)-TODAY()</f>
         <v>27</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B12" s="8"/>
+      <c r="M11" s="5"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B12" s="7"/>
       <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
@@ -1544,32 +1611,22 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="4"/>
-      <c r="H12" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="31"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10">
-        <v>1</v>
-      </c>
-      <c r="R12" s="10">
-        <v>2</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-      <c r="T12" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B13" s="8"/>
+      <c r="H12" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="28"/>
+      <c r="J12" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="5">
+        <f ca="1">K4/K11</f>
+        <v>0.87037037037037035</v>
+      </c>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B13" s="7"/>
       <c r="C13" s="3" t="s">
         <v>1</v>
       </c>
@@ -1582,28 +1639,16 @@
       <c r="F13" s="4">
         <v>0.5</v>
       </c>
-      <c r="G13" s="30"/>
-      <c r="H13" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K13" s="6">
-        <f ca="1">K4/K11</f>
-        <v>0.87037037037037035</v>
-      </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B14" s="8"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="28"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+    </row>
+    <row r="14" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="7"/>
       <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
@@ -1616,22 +1661,17 @@
       <c r="F14" s="4">
         <v>0.5</v>
       </c>
-      <c r="G14" s="30"/>
-      <c r="H14" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="31"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B15" s="8"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="28"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="7"/>
       <c r="C15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1644,23 +1684,23 @@
       <c r="F15" s="4">
         <v>1</v>
       </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="31"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.4">
-      <c r="B16" s="8" t="s">
+      <c r="G15" s="27"/>
+      <c r="H15" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="28"/>
+      <c r="J15" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="35"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B16" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1675,16 +1715,35 @@
       <c r="F16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="30"/>
-      <c r="H16" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="31"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="O16" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="P16" s="40" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B17" s="7"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="3" t="s">
         <v>7</v>
       </c>
@@ -1697,32 +1756,70 @@
       <c r="F17" s="4">
         <v>1</v>
       </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="32"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="29"/>
+      <c r="J17" s="41">
+        <v>1</v>
+      </c>
+      <c r="K17" s="12">
+        <v>2</v>
+      </c>
+      <c r="L17" s="12">
+        <v>3</v>
+      </c>
+      <c r="M17" s="12">
+        <v>4</v>
+      </c>
+      <c r="N17" s="12">
+        <v>5</v>
+      </c>
+      <c r="O17" s="12">
+        <v>6</v>
+      </c>
+      <c r="P17" s="42">
+        <v>7</v>
+      </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" s="6"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="41">
+        <v>8</v>
+      </c>
+      <c r="K18" s="12">
+        <v>9</v>
+      </c>
+      <c r="L18" s="12">
+        <v>10</v>
+      </c>
+      <c r="M18" s="12">
+        <v>11</v>
+      </c>
+      <c r="N18" s="12">
+        <v>12</v>
+      </c>
+      <c r="O18" s="12">
+        <v>13</v>
+      </c>
+      <c r="P18" s="42">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B19" s="7"/>
+      <c r="B19" s="6"/>
       <c r="C19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1732,41 +1829,79 @@
       <c r="E19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <v>1</v>
       </c>
       <c r="G19" s="2"/>
-      <c r="H19" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I19" s="6"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
+      <c r="H19" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="43">
+        <v>15</v>
+      </c>
+      <c r="K19" s="12">
+        <v>16</v>
+      </c>
+      <c r="L19" s="52">
+        <v>17</v>
+      </c>
+      <c r="M19" s="52">
+        <v>18</v>
+      </c>
+      <c r="N19" s="52">
+        <v>19</v>
+      </c>
+      <c r="O19" s="53">
+        <v>20</v>
+      </c>
+      <c r="P19" s="54">
+        <v>21</v>
+      </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B20" s="7"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="8">
         <v>1</v>
       </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B21" s="7" t="s">
+      <c r="H20" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="55">
+        <v>22</v>
+      </c>
+      <c r="K20" s="52">
+        <v>23</v>
+      </c>
+      <c r="L20" s="52">
+        <v>24</v>
+      </c>
+      <c r="M20" s="52">
+        <v>25</v>
+      </c>
+      <c r="N20" s="52">
+        <v>26</v>
+      </c>
+      <c r="O20" s="53">
+        <v>27</v>
+      </c>
+      <c r="P20" s="54">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="3"/>
@@ -1774,15 +1909,26 @@
       <c r="E21" s="1"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B22" s="7"/>
+      <c r="H21" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="56">
+        <v>29</v>
+      </c>
+      <c r="K21" s="57">
+        <v>30</v>
+      </c>
+      <c r="L21" s="57">
+        <v>31</v>
+      </c>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="46"/>
+    </row>
+    <row r="22" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="6"/>
       <c r="C22" s="3" t="s">
         <v>12</v>
       </c>
@@ -1792,18 +1938,18 @@
       <c r="E22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="8">
         <v>1</v>
       </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B23" s="7"/>
+      <c r="H22" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="6"/>
       <c r="C23" s="3" t="s">
         <v>13</v>
       </c>
@@ -1813,24 +1959,21 @@
       <c r="E23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>1</v>
       </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J23" s="11"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B24" s="7" t="s">
+      <c r="H23" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="3"/>
@@ -1838,20 +1981,29 @@
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J24" s="11"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B25" s="7"/>
+      <c r="H24" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" s="49"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="58">
+        <v>1</v>
+      </c>
+      <c r="N24" s="58">
+        <v>2</v>
+      </c>
+      <c r="O24" s="58">
+        <v>3</v>
+      </c>
+      <c r="P24" s="59">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B25" s="6"/>
       <c r="C25" s="3" t="s">
         <v>15</v>
       </c>
@@ -1861,24 +2013,39 @@
       <c r="E25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="8">
         <v>1</v>
       </c>
       <c r="G25" s="2"/>
-      <c r="H25" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B26" s="7"/>
+      <c r="H25" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="60">
+        <v>5</v>
+      </c>
+      <c r="K25" s="61">
+        <v>6</v>
+      </c>
+      <c r="L25" s="62">
+        <v>7</v>
+      </c>
+      <c r="M25" s="63">
+        <v>8</v>
+      </c>
+      <c r="N25" s="63">
+        <v>9</v>
+      </c>
+      <c r="O25" s="63">
+        <v>10</v>
+      </c>
+      <c r="P25" s="64">
+        <v>11</v>
+      </c>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B26" s="6"/>
       <c r="C26" s="3" t="s">
         <v>27</v>
       </c>
@@ -1888,24 +2055,39 @@
       <c r="E26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="8">
         <v>1</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="J26" s="11"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+      <c r="H26" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="41">
+        <v>12</v>
+      </c>
+      <c r="K26" s="65">
+        <v>13</v>
+      </c>
+      <c r="L26" s="12">
+        <v>14</v>
+      </c>
+      <c r="M26" s="12">
+        <v>15</v>
+      </c>
+      <c r="N26" s="12">
+        <v>16</v>
+      </c>
+      <c r="O26" s="12">
+        <v>17</v>
+      </c>
+      <c r="P26" s="42">
+        <v>18</v>
+      </c>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="3"/>
@@ -1913,12 +2095,33 @@
       <c r="E27" s="1"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B28" s="7"/>
+      <c r="H27" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="41">
+        <v>19</v>
+      </c>
+      <c r="K27" s="33">
+        <v>20</v>
+      </c>
+      <c r="L27" s="12">
+        <v>21</v>
+      </c>
+      <c r="M27" s="12">
+        <v>22</v>
+      </c>
+      <c r="N27" s="12">
+        <v>23</v>
+      </c>
+      <c r="O27" s="12">
+        <v>24</v>
+      </c>
+      <c r="P27" s="42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="6"/>
       <c r="C28" s="3" t="s">
         <v>1</v>
       </c>
@@ -1932,12 +2135,29 @@
         <v>2</v>
       </c>
       <c r="G28" s="2"/>
-      <c r="H28" s="20" t="s">
-        <v>39</v>
-      </c>
+      <c r="H28" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="50">
+        <v>26</v>
+      </c>
+      <c r="K28" s="45">
+        <v>27</v>
+      </c>
+      <c r="L28" s="44">
+        <v>28</v>
+      </c>
+      <c r="M28" s="44">
+        <v>29</v>
+      </c>
+      <c r="N28" s="44">
+        <v>30</v>
+      </c>
+      <c r="O28" s="44"/>
+      <c r="P28" s="46"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B29" s="7"/>
+      <c r="B29" s="6"/>
       <c r="C29" s="3" t="s">
         <v>19</v>
       </c>
@@ -1951,12 +2171,14 @@
         <v>2</v>
       </c>
       <c r="G29" s="2"/>
-      <c r="H29" s="20" t="s">
-        <v>39</v>
-      </c>
+      <c r="H29" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B30" s="7"/>
+      <c r="B30" s="6"/>
       <c r="C30" s="3" t="s">
         <v>20</v>
       </c>
@@ -1970,12 +2192,14 @@
         <v>2</v>
       </c>
       <c r="G30" s="2"/>
-      <c r="H30" s="20" t="s">
-        <v>39</v>
-      </c>
+      <c r="H30" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="3"/>
@@ -1983,12 +2207,17 @@
       <c r="E31" s="1"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="20" t="s">
-        <v>39</v>
-      </c>
+      <c r="H31" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J31" s="66" t="s">
+        <v>35</v>
+      </c>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B32" s="7"/>
+      <c r="B32" s="6"/>
       <c r="C32" s="3" t="s">
         <v>44</v>
       </c>
@@ -2002,12 +2231,17 @@
         <v>1</v>
       </c>
       <c r="G32" s="2"/>
-      <c r="H32" s="20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B33" s="7"/>
+      <c r="H32" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J32" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B33" s="6"/>
       <c r="C33" s="3" t="s">
         <v>41</v>
       </c>
@@ -2021,12 +2255,17 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="2"/>
-      <c r="H33" s="20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B34" s="7"/>
+      <c r="H33" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B34" s="6"/>
       <c r="C34" s="3" t="s">
         <v>42</v>
       </c>
@@ -2040,13 +2279,17 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="2"/>
-      <c r="H34" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="K34" s="5"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B35" s="7"/>
+      <c r="H34" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B35" s="6"/>
       <c r="C35" s="3" t="s">
         <v>45</v>
       </c>
@@ -2060,121 +2303,121 @@
         <v>1</v>
       </c>
       <c r="G35" s="2"/>
-      <c r="H35" s="20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
+      <c r="H35" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
     </row>
     <row r="50" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
     </row>
     <row r="51" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
     </row>
     <row r="52" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
     </row>
     <row r="53" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
     </row>
     <row r="54" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
     </row>
     <row r="55" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
     </row>
     <row r="56" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
     </row>
     <row r="57" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
     </row>
     <row r="58" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
     </row>
     <row r="59" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
     </row>
     <row r="60" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
     </row>
     <row r="61" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
     </row>
     <row r="62" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
     </row>
     <row r="63" spans="4:5" x14ac:dyDescent="0.4">
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
